--- a/zy70862/对账完整报告_测试.xlsx
+++ b/zy70862/对账完整报告_测试.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -584,7 +584,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DIFF_20260520070914103694_1_0</t>
+          <t>DIFF_20260522195700041503_1_0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-20T07:09:14.122533</t>
+          <t>2026-05-22T19:57:00.084065</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DIFF_20260520070914103950_2_0</t>
+          <t>DIFF_20260522195700043465_2_0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -694,7 +694,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DIFF_20260520070914103950_2_1</t>
+          <t>DIFF_20260522195700043465_2_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DIFF_20260520070914104438_4_0</t>
+          <t>DIFF_20260522195700045683_4_0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEG_20260520070914115377_4</t>
+          <t>NEG_20260522195700061104_4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/zy70862/对账完整报告_测试.xlsx
+++ b/zy70862/对账完整报告_测试.xlsx
@@ -584,7 +584,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DIFF_20260522195700041503_1_0</t>
+          <t>DIFF_20260522201259788737_1_0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-22T19:57:00.084065</t>
+          <t>2026-05-22T20:12:59.801304</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DIFF_20260522195700043465_2_0</t>
+          <t>DIFF_20260522201259788980_2_0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -694,7 +694,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DIFF_20260522195700043465_2_1</t>
+          <t>DIFF_20260522201259788980_2_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DIFF_20260522195700045683_4_0</t>
+          <t>DIFF_20260522201259789442_4_0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEG_20260522195700061104_4</t>
+          <t>NEG_20260522201259787644_4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
